--- a/basedatos_partidas/salida/descompuestos/CT-09-02-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-09-02-010.xlsx
@@ -539,10 +539,10 @@
         <v>1.06</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="H10" t="n">
-        <v>7.21</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>1.05</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.41</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>11.62</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="13">
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.62</v>
+        <v>23.09</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>14.77</v>
+        <v>23.32</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-09-02-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-09-02-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 09 Cielos rasos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Cielos desmontables y registrables</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
